--- a/data/trans_dic/IP21B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -736,7 +737,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 73,66</t>
+          <t>0,0; 68,55</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -751,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,97</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,77</t>
+          <t>0,0; 31,27</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,44</t>
+          <t>0,0; 85,77</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,78</t>
+          <t>0,0; 78,39</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,38</t>
+          <t>0,0; 81,78</t>
         </is>
       </c>
     </row>
@@ -856,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 91,11</t>
+          <t>0,0; 84,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -881,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,03</t>
+          <t>0,0; 36,49</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,0</t>
+          <t>0,0; 83,69</t>
         </is>
       </c>
     </row>
@@ -996,57 +997,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,59</t>
+          <t>0,0; 63,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,94</t>
+          <t>0,0; 81,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,44</t>
+          <t>0,0; 57,02</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,64</t>
+          <t>0,0; 56,28</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,56</t>
+          <t>0,0; 39,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,6; 39,97</t>
+          <t>4,65; 42,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,88</t>
+          <t>0,0; 75,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,59; 43,81</t>
+          <t>5,8; 45,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,36</t>
+          <t>0,0; 83,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 76,51</t>
+          <t>0,0; 72,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,02</t>
+          <t>0,0; 24,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,03; 32,97</t>
+          <t>8,1; 33,43</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,26; 67,15</t>
+          <t>8,64; 66,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,46</t>
+          <t>0,0; 52,51</t>
         </is>
       </c>
     </row>
@@ -1276,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,34</t>
+          <t>0,0; 74,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,68</t>
+          <t>0,0; 67,58</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,99; 69,49</t>
+          <t>10,89; 68,81</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1296,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,68</t>
+          <t>0,0; 51,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,12; 82,08</t>
+          <t>12,29; 82,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,09</t>
+          <t>0,0; 36,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 43,16</t>
+          <t>4,75; 40,88</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16,93; 64,54</t>
+          <t>17,51; 64,44</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,11</t>
+          <t>0,0; 58,43</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,37</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,87</t>
+          <t>0,0; 64,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,64</t>
+          <t>0,0; 58,92</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,39</t>
+          <t>0,0; 45,05</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,92</t>
+          <t>0,0; 45,96</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,63</t>
+          <t>0,0; 83,45</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,65</t>
+          <t>0,0; 17,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,43; 27,77</t>
+          <t>5,39; 29,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,85; 43,96</t>
+          <t>10,87; 42,64</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,57; 51,97</t>
+          <t>6,65; 52,35</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,33; 22,02</t>
+          <t>4,25; 22,18</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 32,2</t>
+          <t>10,14; 32,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,93; 40,87</t>
+          <t>9,39; 41,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 54,06</t>
+          <t>6,14; 52,31</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,75; 16,2</t>
+          <t>3,54; 15,9</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,62; 26,27</t>
+          <t>9,76; 25,46</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13,34; 34,31</t>
+          <t>14,1; 36,25</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,04; 43,04</t>
+          <t>12,21; 45,42</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>590</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>667</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1515</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1941</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1842</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2723</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1963</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1831</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2582</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2962</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2673</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2957</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3618</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>831</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2164</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2224</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2945</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2681</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1321</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>621</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3465</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3304</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3494</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3423</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 1482</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2696</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1465</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>712</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4646</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2924</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>809</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2800</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>676; 6131</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3257</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>589; 4578</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3649</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3459</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4176</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2002; 8258</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>749; 5740</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3413</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>734</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1985</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>2386</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>527</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4371</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2336</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2790</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>614; 3882</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2230</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3540</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>709; 4740</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2889</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>522; 4497</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>1998; 7354</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3051</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>682</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>615</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2483</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2648</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2744</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2727</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2775</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2601</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3430</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4778</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2243</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>5855</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>3201</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>4635</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>9284</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>9171</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>5443</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4114</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>1360; 7462</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2088; 8191</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>613; 4824</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>1325; 6920</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>3097; 9784</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1944; 8486</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>765; 6519</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>1939; 8707</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>5442; 14197</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5627; 14466</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>2647; 9845</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP21B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Clase-trans_dic.xlsx
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>0,0; 83,97</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,27</t>
+          <t>0,0; 35,93</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 85,77</t>
+          <t>0,0; 80,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,39</t>
+          <t>0,0; 78,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,78</t>
+          <t>0,0; 80,61</t>
         </is>
       </c>
     </row>
@@ -897,7 +897,7 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,49</t>
+          <t>0,0; 35,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,69</t>
+          <t>0,0; 83,61</t>
         </is>
       </c>
     </row>
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,0</t>
+          <t>0,0; 63,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 81,75</t>
+          <t>0,0; 83,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,02</t>
+          <t>0,0; 56,76</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,28</t>
+          <t>0,0; 64,47</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,25</t>
+          <t>0,0; 39,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,65; 42,15</t>
+          <t>4,63; 38,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,76</t>
+          <t>0,0; 82,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,8; 45,09</t>
+          <t>5,78; 49,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,5</t>
+          <t>0,0; 68,89</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 72,2</t>
+          <t>0,0; 64,75</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,36</t>
+          <t>0,0; 20,52</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,1; 33,43</t>
+          <t>8,11; 35,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 66,21</t>
+          <t>8,62; 65,57</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,51</t>
+          <t>0,0; 53,62</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,55</t>
+          <t>0,0; 75,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,58</t>
+          <t>0,0; 69,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,89; 68,81</t>
+          <t>10,79; 69,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1302,12 +1302,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,49</t>
+          <t>0,0; 55,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>12,29; 82,12</t>
+          <t>12,02; 82,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,61</t>
+          <t>0,0; 36,36</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,75; 40,88</t>
+          <t>5,01; 42,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17,51; 64,44</t>
+          <t>18,47; 65,14</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,43</t>
+          <t>0,0; 66,24</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,05</t>
+          <t>0,0; 43,52</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,96</t>
+          <t>0,0; 46,11</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,46</t>
+          <t>0,0; 17,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,39; 29,58</t>
+          <t>5,4; 27,39</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,87; 42,64</t>
+          <t>10,89; 44,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 52,35</t>
+          <t>6,65; 51,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,25; 22,18</t>
+          <t>4,27; 23,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 32,03</t>
+          <t>8,47; 31,96</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,39; 41,0</t>
+          <t>7,71; 39,55</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>6,14; 52,31</t>
+          <t>7,29; 55,16</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,54; 15,9</t>
+          <t>3,94; 15,97</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,76; 25,46</t>
+          <t>9,55; 25,93</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14,1; 36,25</t>
+          <t>12,93; 35,0</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,21; 45,42</t>
+          <t>11,03; 45,71</t>
         </is>
       </c>
     </row>
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2582</t>
+          <t>0; 2168</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
+          <t>0; 3404</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2498</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
           <t>0; 2962</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2673</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2957</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3618</t>
+          <t>0; 3566</t>
         </is>
       </c>
     </row>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2945</t>
+          <t>0; 2888</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2681</t>
+          <t>0; 2678</t>
         </is>
       </c>
     </row>
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3465</t>
+          <t>0; 3473</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3304</t>
+          <t>0; 3382</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3494</t>
+          <t>0; 3478</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3423</t>
+          <t>0; 3922</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2800</t>
+          <t>0; 2805</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>676; 6131</t>
+          <t>674; 5609</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>0; 3549</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>589; 4578</t>
+          <t>587; 5008</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3649</t>
+          <t>0; 3011</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3101</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4176</t>
+          <t>0; 3517</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2002; 8258</t>
+          <t>2003; 8654</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>749; 5740</t>
+          <t>748; 5684</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3413</t>
+          <t>0; 3485</t>
         </is>
       </c>
     </row>
@@ -2759,17 +2759,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2336</t>
+          <t>0; 2364</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2790</t>
+          <t>0; 2873</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>614; 3882</t>
+          <t>609; 3907</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -2784,12 +2784,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3540</t>
+          <t>0; 3833</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>709; 4740</t>
+          <t>694; 4780</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2799,22 +2799,22 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2889</t>
+          <t>0; 2869</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>522; 4497</t>
+          <t>551; 4678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1998; 7354</t>
+          <t>2108; 7433</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3051</t>
+          <t>0; 3459</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2727</t>
+          <t>0; 2634</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2775</t>
+          <t>0; 2784</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4114</t>
+          <t>0; 4203</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1360; 7462</t>
+          <t>1363; 6908</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2088; 8191</t>
+          <t>2092; 8535</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>613; 4824</t>
+          <t>613; 4782</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1325; 6920</t>
+          <t>1333; 7271</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3097; 9784</t>
+          <t>2587; 9764</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1944; 8486</t>
+          <t>1597; 8186</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>765; 6519</t>
+          <t>908; 6874</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1939; 8707</t>
+          <t>2155; 8744</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5442; 14197</t>
+          <t>5326; 14461</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5627; 14466</t>
+          <t>5161; 13968</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2647; 9845</t>
+          <t>2390; 9907</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP21B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP21B-Clase-trans_dic.xlsx
@@ -527,13 +527,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>17,63%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33,98%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>29,97%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34,95%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>27,61%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>32,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>17,63%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,98%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>35,83%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>34,33%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 73,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 100,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 83,1</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 68,55</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 100,0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 83,97</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,93</t>
+          <t>0,0; 31,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,17</t>
+          <t>0,0; 81,44</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,52</t>
+          <t>0,0; 78,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 80,61</t>
+          <t>0,0; 72,84</t>
         </is>
       </c>
     </row>
@@ -789,27 +789,27 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>25,18%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32,3%</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -824,27 +824,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
+          <t>35,26%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>9,0%</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>28,13%</t>
         </is>
       </c>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 77,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -872,12 +872,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 84,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -892,12 +892,12 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 86,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,79</t>
+          <t>0,0; 42,03</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,61</t>
+          <t>0,0; 86,14</t>
         </is>
       </c>
     </row>
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24,62%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>32,68%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>32,68%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>22,1%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 63,59</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 81,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,12 +1017,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 63,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1037,12 +1037,12 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 56,76</t>
+          <t>0,0; 56,44</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,47</t>
+          <t>0,0; 55,64</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>19,21%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>33,4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>18,57%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>9,99%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>18,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>34,07%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>33,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>13,97%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,63; 38,56</t>
+          <t>5,59; 43,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,56</t>
+          <t>0,0; 83,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 80,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 56,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,78; 49,32</t>
+          <t>4,6; 39,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 68,89</t>
+          <t>0,0; 82,88</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,52</t>
+          <t>0,0; 17,02</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>8,11; 35,04</t>
+          <t>8,03; 32,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,62; 65,57</t>
+          <t>9,26; 67,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,62</t>
+          <t>0,0; 56,54</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>17,95%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>41,33%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>16,81%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>17,78%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>35,19%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>36,87%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>17,95%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>41,33%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>39,14%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,44</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 69,6</t>
+          <t>0,0; 49,68</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10,79; 69,26</t>
+          <t>12,12; 82,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 75,34</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 68,68</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>10,99; 69,49</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 55,75</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>12,02; 82,81</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,36</t>
+          <t>0,0; 29,09</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5,01; 42,52</t>
+          <t>5,01; 43,16</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 65,14</t>
+          <t>16,93; 64,54</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 66,24</t>
+          <t>0,0; 66,1</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>14,65%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>31,88%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,65%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 64,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 58,64</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,17 +1437,17 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 64,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 58,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 81,37</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1457,17 +1457,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,52</t>
+          <t>0,0; 43,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 46,11</t>
+          <t>0,0; 45,92</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 83,45</t>
+          <t>0,0; 80,63</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>19,17%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>21,23%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26,48%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5,26%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>13,6%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>24,87%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>24,34%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10,89%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,17%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>21,23%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,84</t>
+          <t>2,33; 22,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 27,39</t>
+          <t>9,73; 32,2</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10,89; 44,43</t>
+          <t>7,93; 40,87</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,65; 51,89</t>
+          <t>7,75; 55,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,27; 23,31</t>
+          <t>0,0; 16,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,47; 31,96</t>
+          <t>5,43; 27,77</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,71; 39,55</t>
+          <t>10,85; 43,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>7,29; 55,16</t>
+          <t>7,54; 55,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,94; 15,97</t>
+          <t>3,75; 16,2</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9,55; 25,93</t>
+          <t>9,62; 26,27</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12,93; 35,0</t>
+          <t>13,34; 34,31</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,03; 45,71</t>
+          <t>11,63; 44,95</t>
         </is>
       </c>
     </row>
@@ -1669,13 +1669,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados (tasa de respuesta: 99,27%)</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital (tasa de respuesta: 99,27%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,12 +1791,12 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1859,54 +1859,54 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>700</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>549</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>743</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>536</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>590</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>627</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>667</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>549</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>925</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>667</t>
-        </is>
-      </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>1085</t>
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1515</t>
+          <t>1369</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2926</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1963</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
+          <t>0; 1831</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1766</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
           <t>0; 1941</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1842</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2723</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1963</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0; 1831</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2168</t>
+          <t>0; 1863</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3404</t>
+          <t>0; 3010</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 2498</t>
+          <t>0; 2538</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 2962</t>
+          <t>0; 2972</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 3566</t>
+          <t>0; 2905</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2014,27 +2014,27 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,7 +2067,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>726</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2082,34 +2082,34 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>726</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>870</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2164</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 2224</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2130</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 2888</t>
+          <t>0; 3392</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0; 2678</t>
+          <t>0; 2665</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -2222,17 +2222,17 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,12 +2275,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1355</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1321</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -2290,39 +2290,39 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>501</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>1355</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>1321</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>621</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>1355</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>621</t>
+          <t>501</t>
         </is>
       </c>
     </row>
@@ -2343,12 +2343,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3498</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3311</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3473</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 3382</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2383,12 +2383,12 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 3478</t>
+          <t>0; 3459</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3922</t>
+          <t>0; 3385</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 1482</t>
+          <t>0; 1277</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1950</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1460</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>712</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2696</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1465</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1950</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1460</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>862</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2805</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>674; 5609</t>
+          <t>567; 4449</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3549</t>
+          <t>0; 3643</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3727</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4035</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>587; 5008</t>
+          <t>669; 5813</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3011</t>
+          <t>0; 3563</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 3101</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3517</t>
+          <t>0; 2917</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2003; 8654</t>
+          <t>1982; 8144</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>748; 5684</t>
+          <t>803; 5821</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 3485</t>
+          <t>0; 3490</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1234</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2386</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>527</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>734</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1985</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>822</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1234</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>2386</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>860</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>860</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 2364</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2873</t>
+          <t>0; 3415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>609; 3907</t>
+          <t>700; 4738</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 2230</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2361</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 3833</t>
+          <t>0; 2835</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>694; 4780</t>
+          <t>620; 3920</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2197</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 2869</t>
+          <t>0; 2295</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>551; 4678</t>
+          <t>552; 4748</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>2108; 7433</t>
+          <t>1932; 7365</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 3459</t>
+          <t>0; 3129</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,49 +2899,49 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>615</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>682</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
           <t>792</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>615</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>682</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>846</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
           <t>683</t>
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>846</t>
+          <t>893</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2644</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2732</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 2483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,17 +2987,17 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2648</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 2744</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2020</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -3007,17 +3007,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 2634</t>
+          <t>0; 2626</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 2784</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 2601</t>
+          <t>0; 2513</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>3396</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>5855</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>4394</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2999</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>1239</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>3430</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>4778</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2243</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>3396</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5855</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>4394</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3201</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5356</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 4203</t>
+          <t>726; 6869</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>1363; 6908</t>
+          <t>2974; 9835</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2092; 8535</t>
+          <t>1642; 8458</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>613; 4782</t>
+          <t>877; 6332</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1333; 7271</t>
+          <t>0; 3923</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>2587; 9764</t>
+          <t>1371; 7005</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1597; 8186</t>
+          <t>2084; 8445</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>908; 6874</t>
+          <t>666; 4896</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2155; 8744</t>
+          <t>2053; 8868</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5326; 14461</t>
+          <t>5365; 14652</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>5161; 13968</t>
+          <t>5323; 13694</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>2390; 9907</t>
+          <t>2344; 9061</t>
         </is>
       </c>
     </row>
